--- a/呉俊鋒_週報_2025年8月分.xlsx
+++ b/呉俊鋒_週報_2025年8月分.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2240651-29CF-432F-897E-FCDC75D2B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4324CA3-0BF0-4C6C-9BB0-18E0AB915F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年8月4日の週" sheetId="6" r:id="rId1"/>
     <sheet name="2025年8月18日の週" sheetId="7" r:id="rId2"/>
+    <sheet name="2025年8月25日の週" sheetId="9" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Holiday">[1]祝日!$A$2:$B$335</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'2025年8月18日の週'!$A$1:$K$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2025年8月25日の週'!$A$1:$K$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'2025年8月4日の週'!$A$1:$K$20</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
   <si>
     <t>所属</t>
     <rPh sb="0" eb="2">
@@ -383,6 +385,103 @@
     </rPh>
     <rPh sb="60" eb="62">
       <t>チャクシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今週の進捗状況：集中管理室画面対応完了、集中管理室データ集計画面着手
+来週の進捗予定：</t>
+    <rPh sb="8" eb="10">
+      <t>シュウチュウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>カンリシツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュウチュウ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カンリシツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シュウケイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>チャクシュ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ライシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・8/25
+　下記の機能実装
+　■集中管理室一覧画面にアラート表示部分追加
+　■集中管理室一覧画面：
+　　・ポップアップ画面追加
+　　・アラートアイコンクリックして、画面ポップアップ
+　　・python側のロジック実装
+　　・自動的に病理室の情報マッチング
+　　・ポップアップ画面表示仕様追加
+・8/26
+　病理診断室画面グラフの表示調整
+　購入した新品M5Stackとセンサー状況確認
+・8/27
+　集中管理室画面関連ソース（Python、JS、HTMLなど）作成
+・8/28
+　M5Stackマニュアル作成
+　集中管理室一覧画面に八つ室のデータ非同期表示
+・8/29
+　ゼックテック佐藤社長に現状報告
+　集中管理室一覧画面にアラート部分実装着手</t>
+    <rPh sb="7" eb="9">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="189" eb="191">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="191" eb="193">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="208" eb="210">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="253" eb="255">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="274" eb="277">
+      <t>ヒドウキ</t>
+    </rPh>
+    <rPh sb="293" eb="297">
+      <t>サトウシャチョウ</t>
+    </rPh>
+    <rPh sb="298" eb="302">
+      <t>ゲンジョウホウコク</t>
+    </rPh>
+    <rPh sb="318" eb="320">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="320" eb="322">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4407,4 +4506,308 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07DE883-EAC4-4FFD-BCC5-F47E9772B65F}">
+  <dimension ref="B1:M20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="7.8984375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="16.3984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.09765625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" s="2" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B4" s="13"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B5" s="13"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B6" s="13"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B7" s="13"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="2:13" ht="364.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="30"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B10" s="13"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B11" s="13"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B12" s="13"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B13" s="13"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="2:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="30"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B15" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B16" s="13"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" s="13"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B19" s="13"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20" spans="2:11" ht="147.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="14"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="C15:K20"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:K8"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="C9:K14"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/呉俊鋒_週報_2025年8月分.xlsx
+++ b/呉俊鋒_週報_2025年8月分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4324CA3-0BF0-4C6C-9BB0-18E0AB915F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FA71E6-EE29-40F1-A2A5-0BC027A00C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
   <si>
     <t>所属</t>
     <rPh sb="0" eb="2">
@@ -389,41 +389,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>今週の進捗状況：集中管理室画面対応完了、集中管理室データ集計画面着手
-来週の進捗予定：</t>
-    <rPh sb="8" eb="10">
-      <t>シュウチュウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カンリシツ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シュウチュウ</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>カンリシツ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シュウケイ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>チャクシュ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ライシュウ</t>
-    </rPh>
+    <t>　</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -437,8 +403,11 @@
 　　・自動的に病理室の情報マッチング
 　　・ポップアップ画面表示仕様追加
 ・8/26
-　病理診断室画面グラフの表示調整
-　購入した新品M5Stackとセンサー状況確認
+　■集中管理室一覧画面：
+　　・ポップアップ画面は窓口形で表示破棄、モーダルの形に変更
+　　・ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ解決
+　　・ポップアップ画面内容調整
+　　・各同期・非同期リクエストをRestful式に調整中
 ・8/27
 　集中管理室画面関連ソース（Python、JS、HTMLなど）作成
 ・8/28
@@ -456,32 +425,117 @@
     <rPh sb="12" eb="14">
       <t>ジッソウ</t>
     </rPh>
-    <rPh sb="189" eb="191">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="191" eb="193">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="208" eb="210">
+    <rPh sb="244" eb="246">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="246" eb="248">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="252" eb="253">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="253" eb="255">
+      <t>ドウキ</t>
+    </rPh>
+    <rPh sb="256" eb="259">
+      <t>ヒドウキ</t>
+    </rPh>
+    <rPh sb="272" eb="273">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="274" eb="277">
+      <t>チョウセイチュウ</t>
+    </rPh>
+    <rPh sb="292" eb="294">
       <t>カンレン</t>
     </rPh>
-    <rPh sb="253" eb="255">
+    <rPh sb="337" eb="339">
       <t>サクセイ</t>
     </rPh>
-    <rPh sb="274" eb="277">
+    <rPh sb="358" eb="361">
       <t>ヒドウキ</t>
     </rPh>
-    <rPh sb="293" eb="297">
+    <rPh sb="377" eb="381">
       <t>サトウシャチョウ</t>
     </rPh>
-    <rPh sb="298" eb="302">
+    <rPh sb="382" eb="386">
       <t>ゲンジョウホウコク</t>
     </rPh>
-    <rPh sb="318" eb="320">
+    <rPh sb="402" eb="404">
       <t>ブブン</t>
     </rPh>
-    <rPh sb="320" eb="322">
+    <rPh sb="404" eb="406">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ
+　・ポップアップ画面モーダル表示の本質は既存DOMにタグを追加していることです。つまり、グローバルCSS仕様があれば、お互い影響されます。
+　・解決策：iframeタグを利用して、モーダル画面の仕様と既存画面の仕様が隔離できます。但し、モーダルを閉じるときは、iframeの中身をクリアしたほうがいいです。</t>
+    <rPh sb="40" eb="42">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ホンシツ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>サク</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>カクリ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="155" eb="156">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ナカミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4647,7 +4701,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -4723,7 +4777,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>

--- a/呉俊鋒_週報_2025年8月分.xlsx
+++ b/呉俊鋒_週報_2025年8月分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FA71E6-EE29-40F1-A2A5-0BC027A00C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD0BED3-4ACB-4260-ABCA-308ECCCC8C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -393,6 +393,76 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ
+　・ポップアップ画面モーダル表示の本質は既存DOMにタグを追加していることです。つまり、グローバルCSS仕様があれば、お互い影響されます。
+　・解決策：iframeタグを利用して、モーダル画面の仕様と既存画面の仕様が隔離できます。但し、モーダルを閉じるときは、iframeの中身をクリアしたほうがいいです。</t>
+    <rPh sb="40" eb="42">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ホンシツ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>サク</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="129" eb="131">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>カクリ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="155" eb="156">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ナカミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・8/25
 　下記の機能実装
 　■集中管理室一覧画面にアラート表示部分追加
@@ -409,7 +479,11 @@
 　　・ポップアップ画面内容調整
 　　・各同期・非同期リクエストをRestful式に調整中
 ・8/27
-　集中管理室画面関連ソース（Python、JS、HTMLなど）作成
+　■集中管理室一覧画面：
+　　・すべてのリクエストはRestfulに変更
+　　・集中管理室画面のポップアップ画面にグラフ表示追加
+　　・bootstrapのライブラリファイル追加
+　　・集中管理室データ集計画面のPython（仮データ実装）
 ・8/28
 　M5Stackマニュアル作成
 　集中管理室一覧画面に八つ室のデータ非同期表示
@@ -446,96 +520,32 @@
     <rPh sb="274" eb="277">
       <t>チョウセイチュウ</t>
     </rPh>
-    <rPh sb="292" eb="294">
-      <t>カンレン</t>
-    </rPh>
-    <rPh sb="337" eb="339">
+    <rPh sb="387" eb="389">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="397" eb="398">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="401" eb="403">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="424" eb="426">
       <t>サクセイ</t>
     </rPh>
-    <rPh sb="358" eb="361">
+    <rPh sb="445" eb="448">
       <t>ヒドウキ</t>
     </rPh>
-    <rPh sb="377" eb="381">
+    <rPh sb="464" eb="468">
       <t>サトウシャチョウ</t>
     </rPh>
-    <rPh sb="382" eb="386">
+    <rPh sb="469" eb="473">
       <t>ゲンジョウホウコク</t>
     </rPh>
-    <rPh sb="402" eb="404">
+    <rPh sb="489" eb="491">
       <t>ブブン</t>
     </rPh>
-    <rPh sb="404" eb="406">
+    <rPh sb="491" eb="493">
       <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ
-　・ポップアップ画面モーダル表示の本質は既存DOMにタグを追加していることです。つまり、グローバルCSS仕様があれば、お互い影響されます。
-　・解決策：iframeタグを利用して、モーダル画面の仕様と既存画面の仕様が隔離できます。但し、モーダルを閉じるときは、iframeの中身をクリアしたほうがいいです。</t>
-    <rPh sb="40" eb="42">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ホンシツ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>キゾン</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="92" eb="93">
-      <t>タガ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>カイケツ</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>サク</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="126" eb="128">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="129" eb="131">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>キゾン</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="137" eb="139">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>カクリ</t>
-    </rPh>
-    <rPh sb="147" eb="148">
-      <t>タダ</t>
-    </rPh>
-    <rPh sb="155" eb="156">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>ナカミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4622,7 +4632,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -4701,7 +4711,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -4777,7 +4787,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>

--- a/呉俊鋒_週報_2025年8月分.xlsx
+++ b/呉俊鋒_週報_2025年8月分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD0BED3-4ACB-4260-ABCA-308ECCCC8C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9849E7EC-02F1-4D57-A88E-D0B68D270E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,11 +485,9 @@
 　　・bootstrapのライブラリファイル追加
 　　・集中管理室データ集計画面のPython（仮データ実装）
 ・8/28
-　M5Stackマニュアル作成
-　集中管理室一覧画面に八つ室のデータ非同期表示
+　M5StackがPCのIPアドレスにアクセスできるかどうか確認・調査
 ・8/29
-　ゼックテック佐藤社長に現状報告
-　集中管理室一覧画面にアラート部分実装着手</t>
+　</t>
     <rPh sb="7" eb="9">
       <t>カキ</t>
     </rPh>
@@ -529,23 +527,11 @@
     <rPh sb="401" eb="403">
       <t>ジッソウ</t>
     </rPh>
-    <rPh sb="424" eb="426">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="445" eb="448">
-      <t>ヒドウキ</t>
-    </rPh>
-    <rPh sb="464" eb="468">
-      <t>サトウシャチョウ</t>
-    </rPh>
-    <rPh sb="469" eb="473">
-      <t>ゲンジョウホウコク</t>
-    </rPh>
-    <rPh sb="489" eb="491">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="491" eb="493">
-      <t>ジッソウ</t>
+    <rPh sb="441" eb="443">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="444" eb="446">
+      <t>チョウサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4694,7 +4680,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="20"/>
     </row>
-    <row r="8" spans="2:13" ht="364.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="26"/>
       <c r="C8" s="28"/>
       <c r="D8" s="29"/>

--- a/呉俊鋒_週報_2025年8月分.xlsx
+++ b/呉俊鋒_週報_2025年8月分.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pro\GitHub\studyNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9849E7EC-02F1-4D57-A88E-D0B68D270E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C096D21-6271-418C-8469-B46D436063EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,80 +389,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ
-　・ポップアップ画面モーダル表示の本質は既存DOMにタグを追加していることです。つまり、グローバルCSS仕様があれば、お互い影響されます。
-　・解決策：iframeタグを利用して、モーダル画面の仕様と既存画面の仕様が隔離できます。但し、モーダルを閉じるときは、iframeの中身をクリアしたほうがいいです。</t>
-    <rPh sb="40" eb="42">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ホンシツ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>キゾン</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="92" eb="93">
-      <t>タガ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>カイケツ</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>サク</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="126" eb="128">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="129" eb="131">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>キゾン</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="137" eb="139">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="140" eb="142">
-      <t>カクリ</t>
-    </rPh>
-    <rPh sb="147" eb="148">
-      <t>タダ</t>
-    </rPh>
-    <rPh sb="155" eb="156">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>ナカミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・8/25
 　下記の機能実装
 　■集中管理室一覧画面にアラート表示部分追加
@@ -485,8 +411,11 @@
 　　・bootstrapのライブラリファイル追加
 　　・集中管理室データ集計画面のPython（仮データ実装）
 ・8/28
-　M5StackがPCのIPアドレスにアクセスできるかどうか確認・調査
+　■M5Stackデータ転送
+　　・M5StackがPCのIPアドレスにアクセスできるかどうか確認・調査
 ・8/29
+　■M5Stackデータ転送
+　・M5StackでCSVファイルをPCに転送することができる
 　</t>
     <rPh sb="7" eb="9">
       <t>カキ</t>
@@ -527,11 +456,158 @@
     <rPh sb="401" eb="403">
       <t>ジッソウ</t>
     </rPh>
-    <rPh sb="441" eb="443">
+    <rPh sb="423" eb="425">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="458" eb="460">
       <t>カクニン</t>
     </rPh>
-    <rPh sb="444" eb="446">
+    <rPh sb="461" eb="463">
       <t>チョウサ</t>
+    </rPh>
+    <rPh sb="506" eb="508">
+      <t>テンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・8/26
+　■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ
+・8/29
+　■どうやってM5StackはPCにアクセスできるようにするか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・8/26
+　■ポップアップ画面仕様と集中管理室画面仕様がお互いに影響バッグ
+　　・ポップアップ画面モーダル表示の本質は既存DOMにタグを追加していることです。つまり、グローバルCSS仕様があ
+　　　れば、お互い影響されます。
+　　・解決策：iframeタグを利用して、モーダル画面の仕様と既存画面の仕様が隔離できます。但し、モーダルを閉じるとき
+　　　は、iframeの中身をクリアしたほうがいいです。
+・8/29
+　■どうやってM5StackはPCにアクセスできるようにするか？
+　　●調査1：AWS EC2を立ち上げて、IPアドレス公開したら、アクセスできるか？
+　　　・結果：設定がいっぱいがあるし、時間ごとに料金が発生してしまったので、無理です。
+　　●調査2：PCのlocalhost:8000が公開できるか？
+　　　・結果：ngrokを利用して、ローカルPC上で稼働しているネットワーク（TCP）サービスを外部公開できる</t>
+    <rPh sb="48" eb="50">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ホンシツ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="119" eb="120">
+      <t>サク</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="153" eb="155">
+      <t>カクリ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="168" eb="169">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="186" eb="188">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="245" eb="247">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="257" eb="258">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="259" eb="260">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="269" eb="271">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="289" eb="291">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="292" eb="294">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="304" eb="306">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="309" eb="311">
+      <t>リョウキン</t>
+    </rPh>
+    <rPh sb="312" eb="314">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="323" eb="325">
+      <t>ムリ</t>
+    </rPh>
+    <rPh sb="354" eb="356">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="366" eb="368">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="375" eb="377">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今週の進捗状況：集中管理室画面対応完了、集中管理室データ集計画面着手、M5Stackデータ転送調査完了
+来週の進捗予定：HTTPSサービス調査着手、集中管理室データ集計画面続き</t>
+    <rPh sb="47" eb="49">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>チャクシュ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ツヅ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4602,7 +4678,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -4618,7 +4694,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
